--- a/business/products/ContractorJobCostTracker-FREE.xlsx
+++ b/business/products/ContractorJobCostTracker-FREE.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
   <si>
     <t xml:space="preserve">Contractor Job Cost &amp; Cash Flow Tracker - FREE Edition (3 jobs)</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yellow fill = key setting you should review first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula cells are locked so they can't be overwritten by accident. To change a formula: Review &gt; Unprotect Sheet (no password).</t>
   </si>
   <si>
     <t xml:space="preserve">The example rows (jobs J-101 to J-103 and their costs/payments) show the expected format. Overwrite or delete them.</t>
@@ -564,37 +567,37 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -604,17 +607,17 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -907,7 +910,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="B2:B22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -976,23 +979,23 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1002,8 +1005,13 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1032,71 +1040,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>15000</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1500</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>46023</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1132,60 +1141,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>46027</v>
@@ -1222,16 +1231,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="20" t="n">
         <v>46034</v>
@@ -1268,16 +1277,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>46055</v>
@@ -1313,6 +1322,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <conditionalFormatting sqref="N2:N4">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(N2&lt;&gt;"",N2&lt;Settings!$B$5)</formula>
@@ -1353,22 +1363,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1376,16 +1386,16 @@
         <v>46030</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" s="16" t="n">
         <v>6200</v>
@@ -1396,16 +1406,16 @@
         <v>46037</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="21" t="n">
         <v>4100</v>
@@ -1416,16 +1426,16 @@
         <v>46036</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="16" t="n">
         <v>7400</v>
@@ -1436,16 +1446,16 @@
         <v>46043</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="21" t="n">
         <v>6900</v>
@@ -1456,16 +1466,16 @@
         <v>46056</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" s="16" t="n">
         <v>3800</v>
@@ -1476,16 +1486,16 @@
         <v>46063</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" s="21" t="n">
         <v>5200</v>
@@ -1496,16 +1506,16 @@
         <v>46071</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>5600</v>
@@ -1516,16 +1526,16 @@
         <v>46085</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" s="21" t="n">
         <v>6100</v>
@@ -1948,6 +1958,7 @@
       <c r="F61" s="21"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
       <formula1>"Labor,Materials,Subcontractors,Equipment,Other"</formula1>
@@ -1985,19 +1996,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,13 +2016,13 @@
         <v>46027</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>14400</v>
@@ -2022,13 +2033,13 @@
         <v>46034</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="21" t="n">
         <v>11000</v>
@@ -2039,13 +2050,13 @@
         <v>46052</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>11000</v>
@@ -2056,13 +2067,13 @@
         <v>46055</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>15250</v>
@@ -2073,13 +2084,13 @@
         <v>46073</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>19200</v>
@@ -2471,6 +2482,7 @@
       <c r="E61" s="21"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B61" type="list">
       <formula1>Jobs!$A$2:$A$4</formula1>
@@ -2514,37 +2526,37 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,6 +2698,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <conditionalFormatting sqref="K4:K6">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"OVER BUDGET"</formula>
